--- a/Data/Bronze/Syllabus/EnfGeomatica/Análisis espacial.xlsx
+++ b/Data/Bronze/Syllabus/EnfGeomatica/Análisis espacial.xlsx
@@ -2487,49 +2487,113 @@
       <c r="J37" s="48"/>
     </row>
     <row r="38" spans="1:10" s="23" customFormat="1">
-      <c r="A38" s="67"/>
+      <c r="A38" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aplica técnicas de análisis espacial en modelos de datos vectoriales y raster.</t>
+        </is>
+      </c>
       <c r="B38" s="69"/>
-      <c r="C38" s="58"/>
+      <c r="C38" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D38" s="57"/>
       <c r="E38" s="57"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="64"/>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA01</t>
+        </is>
+      </c>
+      <c r="G38" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementar las principales funciones de análisis espacial (consulta, medición, superposición, proximidad y análisis de redes) sobre modelos de datos vectoriales y raster para resolver problemas geográficos.</t>
+        </is>
+      </c>
       <c r="H38" s="65"/>
       <c r="I38" s="66"/>
       <c r="J38" s="48"/>
     </row>
     <row r="39" spans="1:10" s="23" customFormat="1">
-      <c r="A39" s="67"/>
+      <c r="A39" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analiza fenómenos y procesos geográficos a partir de datos espaciales.</t>
+        </is>
+      </c>
       <c r="B39" s="69"/>
-      <c r="C39" s="57"/>
+      <c r="C39" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Analizar</t>
+        </is>
+      </c>
       <c r="D39" s="57"/>
       <c r="E39" s="57"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="64"/>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA02</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analizar relaciones, patrones y tendencias espaciales mediante técnicas geoestadísticas, de análisis del terreno y de análisis hidrológico, e interpretar sus resultados.</t>
+        </is>
+      </c>
       <c r="H39" s="65"/>
       <c r="I39" s="66"/>
       <c r="J39" s="48"/>
     </row>
     <row r="40" spans="1:10" s="23" customFormat="1">
-      <c r="A40" s="67"/>
+      <c r="A40" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comunica los resultados del análisis espacial como soporte a la toma de decisiones.</t>
+        </is>
+      </c>
       <c r="B40" s="69"/>
-      <c r="C40" s="57"/>
+      <c r="C40" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Evaluar</t>
+        </is>
+      </c>
       <c r="D40" s="57"/>
       <c r="E40" s="57"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="64"/>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA03</t>
+        </is>
+      </c>
+      <c r="G40" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presentar y argumentar los resultados de un análisis espacial mediante técnicas de visualización en 2D, 2.5D y 3D, como soporte para la toma de decisiones.</t>
+        </is>
+      </c>
       <c r="H40" s="65"/>
       <c r="I40" s="66"/>
       <c r="J40" s="48"/>
     </row>
     <row r="41" spans="1:10" s="23" customFormat="1">
-      <c r="A41" s="67"/>
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construye modelos de geoprocesamiento y herramientas automatizadas de análisis espacial.</t>
+        </is>
+      </c>
       <c r="B41" s="69"/>
-      <c r="C41" s="57"/>
+      <c r="C41" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Crear</t>
+        </is>
+      </c>
       <c r="D41" s="57"/>
       <c r="E41" s="57"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="67"/>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA04</t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseñar modelos de geoprocesamiento y de análisis multicriterio, y automatizarlos mediante scripts en Python, para la solución de un problema geográfico real.</t>
+        </is>
+      </c>
       <c r="H41" s="68"/>
       <c r="I41" s="69"/>
       <c r="J41" s="48"/>
@@ -2932,12 +2996,28 @@
       </c>
       <c r="B69" s="84"/>
       <c r="C69" s="84"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
+      <c r="D69" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHP</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHP</t>
+        </is>
+      </c>
       <c r="F69" s="28"/>
       <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
+      <c r="H69" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
+      <c r="I69" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOP</t>
+        </is>
+      </c>
       <c r="J69" s="87"/>
     </row>
     <row r="70" spans="1:10">
